--- a/backend/plantillas/plantilla_matriculados.xlsx
+++ b/backend/plantillas/plantilla_matriculados.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriculados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,6 +429,16 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sede</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>periodo</t>
         </is>
       </c>
@@ -436,34 +446,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EST001</t>
+          <t>EST1001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ING101</t>
+          <t>750026C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EST002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ING101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2024-1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-1</t>
         </is>
       </c>
     </row>
